--- a/research/traditional_assets/database/data/tunisia/tunisia_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_engineering_construction.xlsx
@@ -636,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1115596854924271</v>
+        <v>0.1776060087972567</v>
       </c>
       <c r="AB2">
-        <v>0.1115596854924271</v>
+        <v>0.1776060087972567</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1115596854924271</v>
+        <v>0.1776060087972567</v>
       </c>
       <c r="AB3">
-        <v>0.1115596854924271</v>
+        <v>0.1776060087972567</v>
       </c>
       <c r="AD3">
         <v>0</v>
